--- a/documentación/FO-IV-159 INFORME DE PROYECTOS DE AULA _V01 SANarte.xlsx
+++ b/documentación/FO-IV-159 INFORME DE PROYECTOS DE AULA _V01 SANarte.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DANIELA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DANIELA\Desktop\Archivos Uni\CARPETA PARA ARQUITECTURA\SANarte\documentación\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05110F43-973E-46CA-8FC2-01F7F249961D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7826BF-A89B-428B-9D2B-FD07DD00FD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INFORME" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="297">
   <si>
     <t>GESTIÓN DE INVESTIGACIÓN E INNOVACIÓN</t>
   </si>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>Resultados del proyecto:</t>
-  </si>
-  <si>
-    <t>Ejemplo: Logros concretos (implementación), evidencias (productos), Impacto en aprendizaje y comunidad (Numero de estudiantes, porcentaje de ejecución de proyecto y actividas) y valoración de habilidades y actitudes desarrolladas.</t>
   </si>
   <si>
     <t>Productos:</t>
@@ -927,10 +924,49 @@
     <t>Proyecto pensado con el objetivo de hacer una plataforma en linea la cual sirva para impulsar el emprendimiento de mi madre</t>
   </si>
   <si>
-    <t>crear un desarrollo de software con el de hacer una plataforma en linea la cual sirva para impulsar el emprendimiento de mi madre</t>
-  </si>
-  <si>
     <t>Aprendizaje Basado en Proyectos (ABP)</t>
+  </si>
+  <si>
+    <t>La falta de una plataforma digital que logre equilibrar la exhibición de alta fidelidad visual con canales de comunicación inmediata y personalizada. Actualmente, los artistas y pequeños emprendimientos enfrentan a obstáculos como la poco visualización de su arte al mundo o redes.</t>
+  </si>
+  <si>
+    <t>¿De qué manera el diseño de una arquitectura basada en microservicios y un modelo de contacto persistente tipo 'Direct-to-Artist' impacta en la experiencia de usuario dentro de una plataforma de exhibición de arte contemporáneo?</t>
+  </si>
+  <si>
+    <t>Porque el arte es un motor de identidad y forma de expresión, pero muchos artistas y emprendedores emergentes emergentes carecen de visualización profesional que valorizá su obra. SANarte se justifica como una plataforma de democratización cultural, permitiendo que artistas locales, contemporáneos y emprendedores accedan a un mercado global sin los costos prohibitivos de una galería física, pero manteniendo el prestigio visual que su trabajo merece.</t>
+  </si>
+  <si>
+    <t>Diseñar y desarrollar una plataforma web integral bajo la marca SAN Arte, que permita la exhibición, catalogación de obras de arte, optimizando el proceso de atención mediante la integración de canales de comunicación directa para potenciar el emprendimiento familiar.</t>
+  </si>
+  <si>
+    <t>Implementar una interfaz de usuario minimalista y de rendimiento que garantice la correcta visualización de las obras.
+Desarrollar un sistema de comunicación persistente vía WhatsApp para reducir los tiempos de respuesta y humanizar la atención al cliente.
+Configurar una arquitectura de microservicios para la gestión eficiente de (obras).
+Establecer un flujo de navegación intuitivo (Story Map) que guíe al usuario desde la exploración de categorías hasta la intención de interación personalizada.</t>
+  </si>
+  <si>
+    <t>Logro Tecnológico: Implementación de una arquitectura escalable.
+Impacto en la Comunidad: Visibilidad digital 24/7 para el catálogo de obras, eliminando las barreras geográficas para la adquisición de arte.
+Valoración de Habilidades: Aplicación práctica de metodologías ágiles (Story Mapping), diseño de experiencia de usuario (UX) y desarrollo Full Stack con microservicios.
+Eficacia de Comunicación: Reducción del ciclo de venta gracias al contacto directo, permitiendo consultas inmediatas sobre disponibilidad.</t>
+  </si>
+  <si>
+    <t>Software SAN Arte: Aplicación Web funcional (Frontend + Backend).
+Documentación Técnica: Repositorio con ADR, esquema de base de datos y diseño de microservicios.
+Manual de Identidad Digital: Guía de uso de la plataforma para la gestión del emprendimiento.
+Mockups de Alta Fidelidad: Prototipos visuales generados para cada escena de la plataforma.</t>
+  </si>
+  <si>
+    <t>CORHUILA</t>
+  </si>
+  <si>
+    <t>INGENIERIA</t>
+  </si>
+  <si>
+    <t>SISTEMAS</t>
+  </si>
+  <si>
+    <t>DANIELA SANABRIA MOSQUERA</t>
   </si>
 </sst>
 </file>
@@ -1619,6 +1655,28 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -1627,31 +1685,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1698,29 +1731,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -1739,6 +1763,18 @@
     </xf>
     <xf numFmtId="14" fontId="23" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2577,27 +2613,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66"/>
-      <c r="B1" s="67"/>
-      <c r="C1" s="78" t="s">
+      <c r="A1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="79"/>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
     </row>
     <row r="2" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="72" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="74"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="73"/>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
@@ -2614,12 +2650,12 @@
       <c r="T2" s="32"/>
     </row>
     <row r="3" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="77"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="76"/>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
@@ -2636,8 +2672,8 @@
       <c r="T3" s="32"/>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
       <c r="C4" s="42" t="s">
         <v>2</v>
       </c>
@@ -2666,12 +2702,12 @@
       <c r="T4" s="32"/>
     </row>
     <row r="5" spans="1:20" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
+      <c r="A5" s="80"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
       <c r="G5" s="32"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
@@ -2688,95 +2724,95 @@
       <c r="T5" s="32"/>
     </row>
     <row r="6" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-    </row>
-    <row r="7" spans="1:20" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="81"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+    </row>
+    <row r="7" spans="1:20" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50">
         <v>1</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="61" t="s">
-        <v>282</v>
-      </c>
-      <c r="E7" s="62"/>
-      <c r="F7" s="63"/>
-    </row>
-    <row r="8" spans="1:20" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="59"/>
+      <c r="D7" s="82" t="s">
+        <v>281</v>
+      </c>
+      <c r="E7" s="83"/>
+      <c r="F7" s="84"/>
+    </row>
+    <row r="8" spans="1:20" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50">
         <v>2</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="89" t="s">
-        <v>285</v>
-      </c>
-      <c r="E8" s="90"/>
-      <c r="F8" s="91"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="85" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8" s="86"/>
+      <c r="F8" s="87"/>
     </row>
     <row r="9" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50">
         <v>3</v>
       </c>
-      <c r="B9" s="59" t="s">
+      <c r="B9" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="61" t="s">
-        <v>283</v>
-      </c>
-      <c r="E9" s="62"/>
-      <c r="F9" s="63"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="82" t="s">
+        <v>282</v>
+      </c>
+      <c r="E9" s="83"/>
+      <c r="F9" s="84"/>
     </row>
     <row r="10" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50">
         <v>5</v>
       </c>
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="92">
+      <c r="C10" s="59"/>
+      <c r="D10" s="88">
         <v>46122</v>
       </c>
-      <c r="E10" s="93"/>
-      <c r="F10" s="94"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="90"/>
     </row>
     <row r="11" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50">
         <v>6</v>
       </c>
-      <c r="B11" s="59" t="s">
+      <c r="B11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="92">
+      <c r="C11" s="59"/>
+      <c r="D11" s="88">
         <v>46164</v>
       </c>
-      <c r="E11" s="93"/>
-      <c r="F11" s="94"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="90"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50">
         <v>8</v>
       </c>
-      <c r="B12" s="59" t="s">
+      <c r="B12" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="59"/>
       <c r="D12" s="51" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E12" s="52"/>
       <c r="F12" s="53"/>
@@ -2785,12 +2821,12 @@
       <c r="A13" s="50">
         <v>9</v>
       </c>
-      <c r="B13" s="59" t="s">
+      <c r="B13" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="60"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="51" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E13" s="52"/>
       <c r="F13" s="53"/>
@@ -2799,10 +2835,10 @@
       <c r="A14" s="50">
         <v>10</v>
       </c>
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="60"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="51">
         <v>7</v>
       </c>
@@ -2813,10 +2849,10 @@
       <c r="A15" s="50">
         <v>11</v>
       </c>
-      <c r="B15" s="59" t="s">
+      <c r="B15" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="60"/>
+      <c r="C15" s="59"/>
       <c r="D15" s="51">
         <v>1</v>
       </c>
@@ -2829,104 +2865,104 @@
         <v>16</v>
       </c>
       <c r="B16" s="57"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
     </row>
     <row r="17" spans="1:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="50">
         <v>12</v>
       </c>
-      <c r="B17" s="59" t="s">
+      <c r="B17" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="61" t="s">
-        <v>285</v>
-      </c>
-      <c r="E17" s="62"/>
-      <c r="F17" s="63"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="82" t="s">
+        <v>286</v>
+      </c>
+      <c r="E17" s="83"/>
+      <c r="F17" s="84"/>
     </row>
     <row r="18" spans="1:7" ht="88.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="50">
         <v>13</v>
       </c>
-      <c r="B18" s="59" t="s">
+      <c r="B18" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="61" t="s">
-        <v>285</v>
-      </c>
-      <c r="E18" s="62"/>
-      <c r="F18" s="63"/>
-    </row>
-    <row r="19" spans="1:7" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="59"/>
+      <c r="D18" s="82" t="s">
+        <v>287</v>
+      </c>
+      <c r="E18" s="83"/>
+      <c r="F18" s="84"/>
+    </row>
+    <row r="19" spans="1:7" ht="100.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="50">
         <v>14</v>
       </c>
-      <c r="B19" s="59" t="s">
+      <c r="B19" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="61" t="s">
-        <v>285</v>
-      </c>
-      <c r="E19" s="62"/>
-      <c r="F19" s="63"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="82" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" s="83"/>
+      <c r="F19" s="84"/>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="57" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="57"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
     </row>
     <row r="21" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="50">
         <v>15</v>
       </c>
-      <c r="B21" s="59" t="s">
+      <c r="B21" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="61" t="s">
-        <v>286</v>
-      </c>
-      <c r="E21" s="62"/>
-      <c r="F21" s="63"/>
-    </row>
-    <row r="22" spans="1:7" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="59"/>
+      <c r="D21" s="82" t="s">
+        <v>289</v>
+      </c>
+      <c r="E21" s="83"/>
+      <c r="F21" s="84"/>
+    </row>
+    <row r="22" spans="1:7" ht="153.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="50">
         <v>16</v>
       </c>
-      <c r="B22" s="59" t="s">
+      <c r="B22" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="61" t="s">
-        <v>286</v>
-      </c>
-      <c r="E22" s="62"/>
-      <c r="F22" s="63"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="82" t="s">
+        <v>290</v>
+      </c>
+      <c r="E22" s="83"/>
+      <c r="F22" s="84"/>
     </row>
     <row r="23" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="50">
         <v>17</v>
       </c>
-      <c r="B23" s="59" t="s">
+      <c r="B23" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="61" t="s">
-        <v>287</v>
-      </c>
-      <c r="E23" s="62"/>
-      <c r="F23" s="63"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="82" t="s">
+        <v>285</v>
+      </c>
+      <c r="E23" s="83"/>
+      <c r="F23" s="84"/>
       <c r="G23" s="43"/>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -2934,106 +2970,106 @@
         <v>24</v>
       </c>
       <c r="B24" s="57"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-    </row>
-    <row r="25" spans="1:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+    </row>
+    <row r="25" spans="1:7" ht="153.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="50">
         <v>18</v>
       </c>
-      <c r="B25" s="59" t="s">
+      <c r="B25" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="82" t="s">
+        <v>291</v>
+      </c>
+      <c r="E25" s="83"/>
+      <c r="F25" s="84"/>
       <c r="G25" s="43"/>
     </row>
-    <row r="26" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="111.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="50">
         <v>19</v>
       </c>
-      <c r="B26" s="83" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="84"/>
-      <c r="D26" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63"/>
+      <c r="B26" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="61"/>
+      <c r="D26" s="82" t="s">
+        <v>292</v>
+      </c>
+      <c r="E26" s="83"/>
+      <c r="F26" s="84"/>
       <c r="G26" s="43"/>
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="57"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
     </row>
     <row r="28" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="50">
         <v>20</v>
       </c>
-      <c r="B28" s="59" t="s">
+      <c r="B28" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="59"/>
+      <c r="D28" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="60"/>
-      <c r="D28" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="55"/>
-      <c r="F28" s="56"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="64"/>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="57"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
     </row>
     <row r="30" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="50">
         <v>21</v>
       </c>
-      <c r="B30" s="59" t="s">
+      <c r="B30" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="59"/>
+      <c r="D30" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="54" t="s">
+      <c r="E30" s="63"/>
+      <c r="F30" s="64"/>
+    </row>
+    <row r="31" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="54"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+    </row>
+    <row r="32" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="55"/>
-      <c r="F30" s="56"/>
-    </row>
-    <row r="31" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="81"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-    </row>
-    <row r="32" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="82" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="82"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
     </row>
     <row r="33" spans="6:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F33" s="1"/>
@@ -5845,24 +5881,15 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C2:F3"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D18:F18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="A20:F20"/>
@@ -5876,21 +5903,30 @@
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C2:F3"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="38" orientation="landscape" r:id="rId1"/>
@@ -5907,20 +5943,20 @@
     <col min="2" max="2" width="22.5546875" customWidth="1"/>
     <col min="3" max="3" width="39.5546875" customWidth="1"/>
     <col min="4" max="4" width="24.5546875" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="5" max="5" width="27.109375" customWidth="1"/>
     <col min="6" max="6" width="18.5546875" customWidth="1"/>
     <col min="7" max="20" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
+      <c r="A1" s="91" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
     </row>
     <row r="2" spans="1:6" ht="3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33"/>
@@ -5932,31 +5968,43 @@
     </row>
     <row r="3" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="A4" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" s="6">
+        <v>6</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1193029148</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
@@ -7017,246 +7065,246 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="87" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
+      <c r="A1" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="C2" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="D2" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="E2" s="45" t="s">
         <v>46</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="C3" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="D3" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="E3" s="47" t="s">
         <v>51</v>
-      </c>
-      <c r="E3" s="47" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="C4" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="D4" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="E4" s="47" t="s">
         <v>56</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A5" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="C5" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="D5" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="E5" s="47" t="s">
         <v>61</v>
-      </c>
-      <c r="E5" s="47" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="C6" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="D6" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="E6" s="47" t="s">
         <v>66</v>
-      </c>
-      <c r="E6" s="47" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A7" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="C7" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="D7" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="E7" s="47" t="s">
         <v>71</v>
-      </c>
-      <c r="E7" s="47" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="42" x14ac:dyDescent="0.3">
       <c r="A8" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="C8" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="D8" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="E8" s="47" t="s">
         <v>76</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="49" t="s">
+      <c r="C9" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="D9" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="E9" s="47" t="s">
         <v>81</v>
-      </c>
-      <c r="E9" s="47" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="49" t="s">
+      <c r="C10" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="D10" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="46" t="s">
-        <v>86</v>
-      </c>
       <c r="E10" s="47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="C11" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="D11" s="46" t="s">
         <v>89</v>
-      </c>
-      <c r="D11" s="46" t="s">
-        <v>90</v>
       </c>
       <c r="E11" s="46"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="C12" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="D12" s="46" t="s">
         <v>93</v>
-      </c>
-      <c r="D12" s="46" t="s">
-        <v>94</v>
       </c>
       <c r="E12" s="46"/>
     </row>
     <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="C13" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="D13" s="46" t="s">
         <v>97</v>
-      </c>
-      <c r="D13" s="46" t="s">
-        <v>98</v>
       </c>
       <c r="E13" s="46"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="B14" s="49" t="s">
+      <c r="C14" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="D14" s="46" t="s">
         <v>101</v>
-      </c>
-      <c r="D14" s="46" t="s">
-        <v>102</v>
       </c>
       <c r="E14" s="46"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="49" t="s">
+      <c r="C15" s="49" t="s">
         <v>104</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>105</v>
       </c>
       <c r="D15" s="46"/>
       <c r="E15" s="46"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="49" t="s">
         <v>106</v>
-      </c>
-      <c r="B16" s="49" t="s">
-        <v>107</v>
       </c>
       <c r="C16" s="46"/>
       <c r="D16" s="46"/>
@@ -7264,10 +7312,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="49" t="s">
         <v>108</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>109</v>
       </c>
       <c r="C17" s="46"/>
       <c r="D17" s="46"/>
@@ -8328,66 +8376,66 @@
   <sheetData>
     <row r="1" spans="1:33" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>115</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>116</v>
       </c>
       <c r="H1" s="12"/>
       <c r="I1" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="N1" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="15" t="s">
         <v>122</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>123</v>
       </c>
       <c r="Q1" s="16"/>
       <c r="R1" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="T1" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="V1" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="X1" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="Z1" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="AB1" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="AB1" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="AC1" s="18"/>
       <c r="AD1" s="18"/>
@@ -8397,66 +8445,66 @@
     </row>
     <row r="2" spans="1:33" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B2" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="H2" s="11"/>
       <c r="I2" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="J2" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="K2" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="L2" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="N2" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="P2" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="Q2" s="10"/>
       <c r="R2" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="T2" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="X2" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="X2" s="9" t="s">
+      <c r="Z2" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="Z2" s="9" t="s">
+      <c r="AB2" s="22" t="s">
         <v>147</v>
-      </c>
-      <c r="AB2" s="22" t="s">
-        <v>148</v>
       </c>
       <c r="AC2" s="22"/>
       <c r="AD2" s="22"/>
@@ -8466,64 +8514,64 @@
     </row>
     <row r="3" spans="1:33" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>154</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>155</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="J3" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="K3" s="36" t="s">
         <v>157</v>
-      </c>
-      <c r="K3" s="36" t="s">
-        <v>158</v>
       </c>
       <c r="L3" s="37"/>
       <c r="N3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="O3" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="P3" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="Q3" s="10"/>
       <c r="R3" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="T3" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="X3" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="Z3" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="AB3" s="22" t="s">
         <v>166</v>
-      </c>
-      <c r="AB3" s="22" t="s">
-        <v>167</v>
       </c>
       <c r="AC3" s="22"/>
       <c r="AD3" s="22"/>
@@ -8533,62 +8581,62 @@
     </row>
     <row r="4" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>171</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>172</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="J4" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="K4" s="24" t="s">
         <v>174</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>175</v>
       </c>
       <c r="L4" s="25"/>
       <c r="N4" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="O4" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="P4" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="P4" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="Q4" s="10"/>
       <c r="R4" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="T4" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="T4" s="9" t="s">
+      <c r="V4" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="X4" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="X4" s="9" t="s">
+      <c r="Z4" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="Z4" s="9" t="s">
+      <c r="AB4" s="22" t="s">
         <v>183</v>
-      </c>
-      <c r="AB4" s="22" t="s">
-        <v>184</v>
       </c>
       <c r="AC4" s="22"/>
       <c r="AD4" s="22"/>
@@ -8598,141 +8646,141 @@
     </row>
     <row r="5" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>187</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>188</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="11"/>
       <c r="I5" s="26"/>
       <c r="J5" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="K5" s="36" t="s">
         <v>189</v>
-      </c>
-      <c r="K5" s="36" t="s">
-        <v>190</v>
       </c>
       <c r="L5" s="37"/>
       <c r="N5" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q5" s="9"/>
       <c r="R5" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="T5" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="T5" s="9" t="s">
+      <c r="V5" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="V5" s="9" t="s">
+      <c r="X5" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="X5" s="9" t="s">
+      <c r="Z5" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="Z5" s="9" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>197</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>198</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>199</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>200</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="11"/>
       <c r="I6" s="26"/>
       <c r="J6" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="K6" s="24" t="s">
         <v>201</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>202</v>
       </c>
       <c r="L6" s="25"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
       <c r="T6" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="V6" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="V6" s="9" t="s">
+      <c r="X6" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="X6" s="9" t="s">
+      <c r="Z6" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="Z6" s="9" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="C7" s="11" t="s">
         <v>208</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>209</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="11"/>
       <c r="I7" s="38"/>
       <c r="J7" s="35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K7" s="39"/>
       <c r="L7" s="37"/>
       <c r="N7" s="28" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
       <c r="T7" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="V7" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="V7" s="9" t="s">
+      <c r="X7" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="X7" s="9" t="s">
+      <c r="Z7" s="9" t="s">
         <v>215</v>
-      </c>
-      <c r="Z7" s="9" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>217</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>218</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="29"/>
@@ -8749,22 +8797,22 @@
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
       <c r="T8" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="V8" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="V8" s="9" t="s">
+      <c r="X8" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="X8" s="9" t="s">
+      <c r="Z8" s="9" t="s">
         <v>221</v>
-      </c>
-      <c r="Z8" s="9" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -8781,16 +8829,16 @@
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
       <c r="T9" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="V9" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="V9" s="9" t="s">
+      <c r="X9" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="X9" s="9" t="s">
+      <c r="Z9" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="Z9" s="9" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -8810,16 +8858,16 @@
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
       <c r="T10" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="V10" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="V10" s="9" t="s">
+      <c r="X10" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="X10" s="9" t="s">
+      <c r="Z10" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="Z10" s="9" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -8833,16 +8881,16 @@
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
       <c r="T11" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="V11" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="V11" s="9" t="s">
+      <c r="X11" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="X11" s="9" t="s">
+      <c r="Z11" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="Z11" s="9" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -8856,16 +8904,16 @@
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="T12" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="V12" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="V12" s="9" t="s">
+      <c r="X12" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="X12" s="9" t="s">
+      <c r="Z12" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="Z12" s="9" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -8879,13 +8927,13 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="T13" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="V13" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="V13" s="9" t="s">
+      <c r="X13" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="X13" s="9" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
@@ -8899,21 +8947,21 @@
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
       <c r="V14" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="X14" s="9" t="s">
         <v>243</v>
-      </c>
-      <c r="X14" s="9" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B15" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="C15" s="30" t="s">
         <v>246</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>247</v>
       </c>
       <c r="I15" s="11"/>
       <c r="J15" s="10"/>
@@ -8924,24 +8972,24 @@
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="V15" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="X15" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="X15" s="9" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B16" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>251</v>
       </c>
       <c r="I16" s="11"/>
       <c r="J16" s="10"/>
@@ -8952,21 +9000,21 @@
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
       <c r="V16" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="X16" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="X16" s="9" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
@@ -8977,19 +9025,19 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
       <c r="V17" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="X17" s="9" t="s">
         <v>255</v>
-      </c>
-      <c r="X17" s="9" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="C18" s="31" t="s">
         <v>257</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>258</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
@@ -8997,17 +9045,17 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="V18" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="X18" s="9" t="s">
         <v>259</v>
-      </c>
-      <c r="X18" s="9" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19" s="31"/>
       <c r="C19" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
@@ -9015,17 +9063,17 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="V19" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="X19" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="X19" s="9" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="31"/>
       <c r="C20" s="31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
@@ -9033,10 +9081,10 @@
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="V20" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="X20" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="X20" s="9" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9049,7 +9097,7 @@
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
       <c r="X21" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9060,7 +9108,7 @@
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="X22" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9071,7 +9119,7 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="X23" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9082,7 +9130,7 @@
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="X24" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9093,7 +9141,7 @@
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="X25" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9104,7 +9152,7 @@
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
       <c r="X26" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9115,7 +9163,7 @@
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="X27" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9126,7 +9174,7 @@
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="X28" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9137,7 +9185,7 @@
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="X29" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9148,7 +9196,7 @@
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
       <c r="X30" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9159,7 +9207,7 @@
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="X31" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9170,7 +9218,7 @@
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="X32" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="9:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9178,7 +9226,7 @@
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="X33" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="9:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9186,7 +9234,7 @@
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="X34" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="9:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9194,7 +9242,7 @@
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="X35" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="9:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13085,12 +13133,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c7b9d0d2-0928-4bc7-b1e7-d815d07dd502" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3b21ab7c-7e7a-493b-a43f-a219844d5b04">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13335,20 +13385,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c7b9d0d2-0928-4bc7-b1e7-d815d07dd502" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3b21ab7c-7e7a-493b-a43f-a219844d5b04">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B9BAF98-50BE-4545-8DD0-8D32ADCB4CBD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAA1D2E8-D888-49D1-AE42-DB5ADBFBA013}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c7b9d0d2-0928-4bc7-b1e7-d815d07dd502"/>
+    <ds:schemaRef ds:uri="3b21ab7c-7e7a-493b-a43f-a219844d5b04"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13373,12 +13424,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAA1D2E8-D888-49D1-AE42-DB5ADBFBA013}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B9BAF98-50BE-4545-8DD0-8D32ADCB4CBD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c7b9d0d2-0928-4bc7-b1e7-d815d07dd502"/>
-    <ds:schemaRef ds:uri="3b21ab7c-7e7a-493b-a43f-a219844d5b04"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>